--- a/Assesment2_Graph_Problem/DevLog assig 2 graph.xlsx
+++ b/Assesment2_Graph_Problem/DevLog assig 2 graph.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Dover\Documents\School\KIT205\KIT205-618797\Assesment2_Graph_Problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A50FCD8-3FC3-4E5C-8EEC-E78B9C7BAE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACC29E1-A876-4686-9F21-F7CD595D28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E01BF87A-8E79-4CC1-91E6-E14A4898A4E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E01BF87A-8E79-4CC1-91E6-E14A4898A4E9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="20" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
   <si>
     <t>Milestone Description</t>
   </si>
@@ -325,12 +330,93 @@
 test_add_edge
 test_all</t>
   </si>
+  <si>
+    <t>Nodes,MaxEdges,AvgPathLength,ConnectedPercent</t>
+  </si>
+  <si>
+    <t>10,5,25.32,41.1</t>
+  </si>
+  <si>
+    <t>10,10,21.11,41.1</t>
+  </si>
+  <si>
+    <t>10,15,20.65,37.8</t>
+  </si>
+  <si>
+    <t>10,20,23.26,45.6</t>
+  </si>
+  <si>
+    <t>50,5,22.04,24.2</t>
+  </si>
+  <si>
+    <t>50,10,22.62,35.4</t>
+  </si>
+  <si>
+    <t>50,15,22.26,41.3</t>
+  </si>
+  <si>
+    <t>50,20,20.39,44.3</t>
+  </si>
+  <si>
+    <t>200,5,25.16,16.8</t>
+  </si>
+  <si>
+    <t>200,10,23.43,31.0</t>
+  </si>
+  <si>
+    <t>200,15,20.17,33.8</t>
+  </si>
+  <si>
+    <t>200,20,19.32,39.8</t>
+  </si>
+  <si>
+    <t>400,5,27.27,12.9</t>
+  </si>
+  <si>
+    <t>400,10,20.33,26.7</t>
+  </si>
+  <si>
+    <t>400,15,21.63,32.2</t>
+  </si>
+  <si>
+    <t>400,20,20.94,37.3</t>
+  </si>
+  <si>
+    <t>Nodes</t>
+  </si>
+  <si>
+    <t>MaxEdges</t>
+  </si>
+  <si>
+    <t>AvgPathLength</t>
+  </si>
+  <si>
+    <t>ConnectedPercent</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of AvgPathLength</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of ConnectedPercent</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +451,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -412,7 +506,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -452,6 +546,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
@@ -473,8 +575,7236 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[DevLog assig 2 graph.xlsx]Sheet4!PivotTable5</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C4BA-4B24-9E1C-BBCED865950E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>21.11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.329999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C4BA-4B24-9E1C-BBCED865950E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>20.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C4BA-4B24-9E1C-BBCED865950E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>23.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.94</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C4BA-4B24-9E1C-BBCED865950E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1928605423"/>
+        <c:axId val="1928593903"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1928605423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928593903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928593903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928605423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[DevLog assig 2 graph.xlsx]Sheet5!PivotTable6</c:name>
+    <c:fmtId val="20"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F88D-455A-84A4-465AC702A154}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>24.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F88D-455A-84A4-465AC702A154}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F88D-455A-84A4-465AC702A154}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.299999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F88D-455A-84A4-465AC702A154}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1928571823"/>
+        <c:axId val="1928574223"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1928571823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928574223"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928574223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928571823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[DevLog assig 2 graph.xlsx]Sheet5!PivotTable6</c:name>
+    <c:fmtId val="25"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4D12-40BF-87F9-A0B069C9913E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>24.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4D12-40BF-87F9-A0B069C9913E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4D12-40BF-87F9-A0B069C9913E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.299999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4D12-40BF-87F9-A0B069C9913E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1928571823"/>
+        <c:axId val="1928574223"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1928571823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928574223"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928574223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928571823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[DevLog assig 2 graph.xlsx]Sheet4!PivotTable5</c:name>
+    <c:fmtId val="14"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-87F1-449B-B029-BB200EB96F97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>21.11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.329999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-87F1-449B-B029-BB200EB96F97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>20.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-87F1-449B-B029-BB200EB96F97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>23.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.94</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-87F1-449B-B029-BB200EB96F97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1928605423"/>
+        <c:axId val="1928593903"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1928605423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928593903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928593903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928605423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>316954</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>139262</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>27919</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>49596</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90EE7EA-D8AF-0F9B-C7F3-A7760A5D8275}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20176F83-FFD1-C9AD-3906-21886E6E4708}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1657089</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>156575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6028FB97-9FAA-44F2-9097-8D26973E8814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2495549</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{501F3028-1930-4ADF-BABF-99B3537D51BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ben Dover" refreshedDate="46179.757784259258" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="16" xr:uid="{D16EA250-4179-40B4-9198-E91703E79643}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="D25:G41" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Nodes" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="400" count="4">
+        <n v="10"/>
+        <n v="50"/>
+        <n v="200"/>
+        <n v="400"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="MaxEdges" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="20" count="4">
+        <n v="5"/>
+        <n v="10"/>
+        <n v="15"/>
+        <n v="20"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="AvgPathLength" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="19.32" maxValue="27.27"/>
+    </cacheField>
+    <cacheField name="ConnectedPercent" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="12.9" maxValue="45.6" count="15">
+        <n v="41.1"/>
+        <n v="37.799999999999997"/>
+        <n v="45.6"/>
+        <n v="24.2"/>
+        <n v="35.4"/>
+        <n v="41.3"/>
+        <n v="44.3"/>
+        <n v="16.8"/>
+        <n v="31"/>
+        <n v="33.799999999999997"/>
+        <n v="39.799999999999997"/>
+        <n v="12.9"/>
+        <n v="26.7"/>
+        <n v="32.200000000000003"/>
+        <n v="37.299999999999997"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="16">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="25.32"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="21.11"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="20.65"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="23.26"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="22.04"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="22.62"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="22.26"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="20.39"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="25.16"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="23.43"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="20.170000000000002"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="19.32"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="27.27"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="20.329999999999998"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="21.63"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="20.94"/>
+    <x v="14"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F140FE16-3431-4748-8BA0-BA9779C03F9F}" name="PivotTable5" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of AvgPathLength" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="12">
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87F47E70-D839-4A5F-A803-A83B75899BFD}" name="PivotTable6" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+  <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="16">
+        <item x="11"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of ConnectedPercent" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="20" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -793,6 +8123,308 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509493C5-387F-4DA8-8B0D-BB7FB60EEA4C}">
+  <dimension ref="A3:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>10</v>
+      </c>
+      <c r="B5" s="17">
+        <v>25.32</v>
+      </c>
+      <c r="C5" s="17">
+        <v>21.11</v>
+      </c>
+      <c r="D5" s="17">
+        <v>20.65</v>
+      </c>
+      <c r="E5" s="17">
+        <v>23.26</v>
+      </c>
+      <c r="F5" s="17">
+        <v>90.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>50</v>
+      </c>
+      <c r="B6" s="17">
+        <v>22.04</v>
+      </c>
+      <c r="C6" s="17">
+        <v>22.62</v>
+      </c>
+      <c r="D6" s="17">
+        <v>22.26</v>
+      </c>
+      <c r="E6" s="17">
+        <v>20.39</v>
+      </c>
+      <c r="F6" s="17">
+        <v>87.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>200</v>
+      </c>
+      <c r="B7" s="17">
+        <v>25.16</v>
+      </c>
+      <c r="C7" s="17">
+        <v>23.43</v>
+      </c>
+      <c r="D7" s="17">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="E7" s="17">
+        <v>19.32</v>
+      </c>
+      <c r="F7" s="17">
+        <v>88.080000000000013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>400</v>
+      </c>
+      <c r="B8" s="17">
+        <v>27.27</v>
+      </c>
+      <c r="C8" s="17">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="D8" s="17">
+        <v>21.63</v>
+      </c>
+      <c r="E8" s="17">
+        <v>20.94</v>
+      </c>
+      <c r="F8" s="17">
+        <v>90.169999999999987</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="17">
+        <v>99.789999999999992</v>
+      </c>
+      <c r="C9" s="17">
+        <v>87.49</v>
+      </c>
+      <c r="D9" s="17">
+        <v>84.71</v>
+      </c>
+      <c r="E9" s="17">
+        <v>83.910000000000011</v>
+      </c>
+      <c r="F9" s="17">
+        <v>355.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCAC6B2-A199-4848-91C6-0B4DBCC52274}">
+  <dimension ref="A3:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="30" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <v>400</v>
+      </c>
+      <c r="F4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>5</v>
+      </c>
+      <c r="B5" s="17">
+        <v>41.1</v>
+      </c>
+      <c r="C5" s="17">
+        <v>24.2</v>
+      </c>
+      <c r="D5" s="17">
+        <v>16.8</v>
+      </c>
+      <c r="E5" s="17">
+        <v>12.9</v>
+      </c>
+      <c r="F5" s="17">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>10</v>
+      </c>
+      <c r="B6" s="17">
+        <v>41.1</v>
+      </c>
+      <c r="C6" s="17">
+        <v>35.4</v>
+      </c>
+      <c r="D6" s="17">
+        <v>31</v>
+      </c>
+      <c r="E6" s="17">
+        <v>26.7</v>
+      </c>
+      <c r="F6" s="17">
+        <v>134.19999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>15</v>
+      </c>
+      <c r="B7" s="17">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C7" s="17">
+        <v>41.3</v>
+      </c>
+      <c r="D7" s="17">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="E7" s="17">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="F7" s="17">
+        <v>145.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>20</v>
+      </c>
+      <c r="B8" s="17">
+        <v>45.6</v>
+      </c>
+      <c r="C8" s="17">
+        <v>44.3</v>
+      </c>
+      <c r="D8" s="17">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="E8" s="17">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="F8" s="17">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="17">
+        <v>165.6</v>
+      </c>
+      <c r="C9" s="17">
+        <v>145.19999999999999</v>
+      </c>
+      <c r="D9" s="17">
+        <v>121.39999999999999</v>
+      </c>
+      <c r="E9" s="17">
+        <v>109.10000000000001</v>
+      </c>
+      <c r="F9" s="17">
+        <v>541.29999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE4D48D-C417-45FE-8518-4215B0DD66E3}">
   <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -802,8 +8434,16 @@
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
     <col min="4" max="4" width="34.140625" customWidth="1"/>
     <col min="5" max="5" width="68.28515625" customWidth="1"/>
-    <col min="6" max="6" width="48.85546875" customWidth="1"/>
-    <col min="7" max="7" width="79.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
@@ -1137,148 +8777,320 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
+      <c r="B24" s="18" t="s">
+        <v>96</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
+    <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>25.32</v>
+      </c>
+      <c r="G26" s="2">
+        <v>41.1</v>
+      </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="D27" s="2">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>21.11</v>
+      </c>
+      <c r="G27" s="2">
+        <v>41.1</v>
+      </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="D28" s="2">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2">
+        <v>20.65</v>
+      </c>
+      <c r="G28" s="2">
+        <v>37.799999999999997</v>
+      </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="D29" s="2">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20</v>
+      </c>
+      <c r="F29" s="2">
+        <v>23.26</v>
+      </c>
+      <c r="G29" s="2">
+        <v>45.6</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="D30" s="1">
+        <v>50</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5</v>
+      </c>
+      <c r="F30" s="1">
+        <v>22.04</v>
+      </c>
+      <c r="G30" s="1">
+        <v>24.2</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="D31">
+        <v>50</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>22.62</v>
+      </c>
+      <c r="G31">
+        <v>35.4</v>
+      </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="D32">
+        <v>50</v>
+      </c>
+      <c r="E32">
+        <v>15</v>
+      </c>
+      <c r="F32">
+        <v>22.26</v>
+      </c>
+      <c r="G32">
+        <v>41.3</v>
+      </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="D33">
+        <v>50</v>
+      </c>
+      <c r="E33">
+        <v>20</v>
+      </c>
+      <c r="F33">
+        <v>20.39</v>
+      </c>
+      <c r="G33">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="D34">
+        <v>200</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>25.16</v>
+      </c>
+      <c r="G34">
+        <v>16.8</v>
+      </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="D35">
+        <v>200</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>23.43</v>
+      </c>
+      <c r="G35">
+        <v>31</v>
+      </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="D36">
+        <v>200</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="F36">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="G36">
+        <v>33.799999999999997</v>
+      </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="D37">
+        <v>200</v>
+      </c>
+      <c r="E37">
+        <v>20</v>
+      </c>
+      <c r="F37">
+        <v>19.32</v>
+      </c>
+      <c r="G37">
+        <v>39.799999999999997</v>
+      </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="D38">
+        <v>400</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>27.27</v>
+      </c>
+      <c r="G38">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="D39">
+        <v>400</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="G39">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="D40">
+        <v>400</v>
+      </c>
+      <c r="E40">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <v>21.63</v>
+      </c>
+      <c r="G40">
+        <v>32.200000000000003</v>
+      </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="D41">
+        <v>400</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>20.94</v>
+      </c>
+      <c r="G41">
+        <v>37.299999999999997</v>
+      </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
@@ -1305,50 +9117,26 @@
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
@@ -1361,5 +9149,6 @@
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/Assesment2_Graph_Problem/DevLog assig 2 graph.xlsx
+++ b/Assesment2_Graph_Problem/DevLog assig 2 graph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Dover\Documents\School\KIT205\KIT205-618797\Assesment2_Graph_Problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACC29E1-A876-4686-9F21-F7CD595D28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757D49F5-87D9-4984-A3C9-33B9529CC650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E01BF87A-8E79-4CC1-91E6-E14A4898A4E9}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="98">
   <si>
     <t>Milestone Description</t>
   </si>
@@ -147,10 +147,6 @@
   </si>
   <si>
     <t xml:space="preserve">test_dijstra - Tests that the algorithm correctlly calculates the min distance between 2 nodes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">moved some of the 0generic code into graph_test added. moved code into graph_test. 
-Adjusted the dataset file. Removed pageRank code </t>
   </si>
   <si>
     <t xml:space="preserve">dijkstra algorith design 
@@ -410,6 +406,14 @@
   </si>
   <si>
     <t>Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moved some of the generic code into graph_test added. moved code into graph_test. 
+Adjusted the dataset file. Removed pageRank code </t>
+  </si>
+  <si>
+    <t>tutorial work 
+GeeksforGeeks 2025, Dijkstra's Shortest Path Algorithm, GeeksforGeeks, viewed 6 June 2026, https://www.geeksforgeeks.org/dsa/dijkstras-shortest-path-algorithm-greedy-algo-7/. - used for understanding and algorithm design</t>
   </si>
 </sst>
 </file>
@@ -8135,15 +8139,15 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -8158,7 +8162,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,7 +8247,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="17">
         <v>99.789999999999992</v>
@@ -8292,15 +8296,15 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -8315,7 +8319,7 @@
         <v>400</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,7 +8404,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="17">
         <v>165.6</v>
@@ -8532,7 +8536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>26</v>
       </c>
@@ -8549,7 +8553,7 @@
         <v>24</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -8572,12 +8576,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="210" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>31</v>
@@ -8589,98 +8593,98 @@
         <v>33</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="13">
         <v>46177</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="13">
         <v>46177</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="D15" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="330" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="13">
         <v>46178</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="75" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="13">
         <v>46178</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>20</v>
@@ -8689,67 +8693,67 @@
         <v>20</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="150" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="13">
         <v>46179</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="240" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="13">
         <v>46179</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="120" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="3">
         <v>46179</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -8778,7 +8782,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -8788,25 +8792,25 @@
     </row>
     <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
@@ -8824,7 +8828,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
@@ -8842,7 +8846,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
@@ -8860,7 +8864,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
@@ -8878,7 +8882,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1">
@@ -8896,7 +8900,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31">
@@ -8914,7 +8918,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32">
@@ -8932,7 +8936,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33">
@@ -8950,7 +8954,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34">
@@ -8968,7 +8972,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35">
@@ -8986,7 +8990,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36">
@@ -9004,7 +9008,7 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37">
@@ -9022,7 +9026,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38">
@@ -9040,7 +9044,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39">
@@ -9058,7 +9062,7 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40">
@@ -9076,7 +9080,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41">
